--- a/Integration Services Project2/notes/STR(DM-Transaction)-Appendix B - Test and PR Summary.xlsx
+++ b/Integration Services Project2/notes/STR(DM-Transaction)-Appendix B - Test and PR Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspaces\STE.2022.CoswinMigration\Integration Services Project2\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59675538-FA78-41E7-88E1-BE87EE626403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94C7477-B88B-4F4B-8540-0C8E694450A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="603">
   <si>
     <t>Test Status</t>
   </si>
@@ -16080,444 +16080,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> MAXIMO.INSPECTIONFORM </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ADD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> STE_PHYSICALBASELINE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>DECIMAL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ALTER</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> MAXIMO.INSPECTIONFORM </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ADD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> STE_FUNCTIONALBASELINE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>DECIMAL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ALTER</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> MAXIMO.INSPQUESTION </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ADD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> STE_SYSTEMLEVEL </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>VARCHAR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ALTER</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>TABLE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> MAXIMO.INSPQUESTION </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ADD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> STE_ISFUNCTIONAL </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>SMALLINT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>DEFAULT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ALTER</t>
-    </r>
-    <r>
-      <rPr>
         <strike/>
         <sz val="10"/>
         <color rgb="FF000000"/>
@@ -16749,14 +16311,670 @@
     </r>
   </si>
   <si>
-    <t>RESIZE INSPFIELDOPTION.DESCRIPTION TO 1000 CHAR.</t>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> MAXIMO.INSPECTIONFORM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> STE_PHYSICALBASELINE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> MAXIMO.INSPECTIONFORM </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> STE_FUNCTIONALBASELINE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>DECIMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> MAXIMO.INSPQUESTION </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> STE_SYSTEMLEVEL </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>VARCHAR</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>50</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> MAXIMO.INSPQUESTION </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> STE_ISFUNCTIONAL </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>SMALLINT</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>DEFAULT</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>RESIZE INSPFIELD.DESCRIPTION TO VARCHAR(500)</t>
+  </si>
+  <si>
+    <t>RESIZE INSPQUESTION.DESCRIPTION TO VARCHAR(500)</t>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> TABLE MAXIMO.INSPECTIONFORM ADD "STE_TEMPLATE" VARCHAR(50);</t>
+    </r>
+  </si>
+  <si>
+    <t>ALTER TABLE MAXIMO.INSPQUESTION ADD "STE_WEIGHTAGE" DECIMAL(8,2);</t>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> TABLE MAXIMO.INSPFIELD ADD "STE_WEIGHTAGE" DECIMAL(8,2);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> TABLE MAXIMO.INSPFIELD ADD "STE_BASELINE" DECIMAL(8,2);</t>
+    </r>
+  </si>
+  <si>
+    <t>RESIZE INSPFIELDRESULT.TXTRESPONSE TO VARCHAR(500)</t>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF956037"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>MAXIMO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>INSPECTIONRESULT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ADD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>STE_RESULTROWSTAMP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BIGINT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -16971,6 +17189,13 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -17158,7 +17383,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -17377,6 +17602,13 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -17392,12 +17624,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -18344,18 +18573,18 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="86" t="s">
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="87"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="88"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="91"/>
       <c r="K3" s="3" t="s">
         <v>61</v>
       </c>
@@ -25341,7 +25570,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB88DB5-3756-408C-974A-7C21E554649F}">
-  <dimension ref="A1:J309"/>
+  <dimension ref="A1:J327"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="56"/>
@@ -27004,11 +27233,11 @@
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B280" s="89" t="s">
-        <v>593</v>
-      </c>
-      <c r="C280" s="90"/>
-      <c r="D280" s="91"/>
+      <c r="B280" s="84" t="s">
+        <v>589</v>
+      </c>
+      <c r="C280" s="85"/>
+      <c r="D280" s="86"/>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B281" s="79" t="s">
@@ -27042,11 +27271,11 @@
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B289" s="89" t="s">
-        <v>594</v>
-      </c>
-      <c r="C289" s="90"/>
-      <c r="D289" s="91"/>
+      <c r="B289" s="84" t="s">
+        <v>590</v>
+      </c>
+      <c r="C289" s="85"/>
+      <c r="D289" s="86"/>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
@@ -27099,38 +27328,142 @@
       <c r="G301" s="73"/>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B303" t="s">
+      <c r="B303" s="79" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B304" s="79" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B305" s="79" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B306" s="79" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="307" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B307" s="79" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B308" s="79" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B309" s="79" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B310" s="79" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B311" s="92" t="s">
+        <v>597</v>
+      </c>
+      <c r="C311" s="92"/>
+      <c r="D311" s="92"/>
+    </row>
+    <row r="312" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B312" s="92" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B304" t="s">
+    <row r="313" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B313" s="92" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" t="s">
+    <row r="314" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B314" s="92" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B306" s="79" t="s">
+    <row r="315" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B315" s="92" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B316" s="93" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B317" s="93" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B318" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B319" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B320" s="84" t="s">
+        <v>591</v>
+      </c>
+      <c r="C320" s="85"/>
+      <c r="D320" s="86"/>
+    </row>
+    <row r="321" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B321" s="84" t="s">
+        <v>592</v>
+      </c>
+      <c r="C321" s="85"/>
+      <c r="D321" s="86"/>
+    </row>
+    <row r="322" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B322" s="84" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B307" s="79" t="s">
+      <c r="C322" s="85"/>
+      <c r="D322" s="86"/>
+    </row>
+    <row r="323" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B323" s="84" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B308" s="79" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B309" s="79" t="s">
-        <v>592</v>
+      <c r="C323" s="85"/>
+      <c r="D323" s="86"/>
+    </row>
+    <row r="324" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B324" s="84" t="s">
+        <v>593</v>
+      </c>
+      <c r="C324" s="85"/>
+      <c r="D324" s="86"/>
+    </row>
+    <row r="325" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B325" s="84" t="s">
+        <v>594</v>
+      </c>
+      <c r="C325" s="85"/>
+      <c r="D325" s="86"/>
+    </row>
+    <row r="326" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="327" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B327" s="79" t="s">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
